--- a/TSOoficios/Registros Algoritmo.xlsx
+++ b/TSOoficios/Registros Algoritmo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moral\Desktop\TSOPIA\TSOoficios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEDCF09-DC43-4C3A-B766-CAFDC8119689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DD39B6-C845-462C-A835-207D0F5F9ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{EBECAEB8-C1FB-400C-8D73-62961D68CFF4}"/>
   </bookViews>
